--- a/docs/StructureDefinition-cumulative-stress-burden.xlsx
+++ b/docs/StructureDefinition-cumulative-stress-burden.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-cumulative-stress-burden.xlsx
+++ b/docs/StructureDefinition-cumulative-stress-burden.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-cumulative-stress-burden.xlsx
+++ b/docs/StructureDefinition-cumulative-stress-burden.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,7 +475,7 @@
     <t>Mission Context</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-cumulative-stress-burden.xlsx
+++ b/docs/StructureDefinition-cumulative-stress-burden.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-cumulative-stress-burden.xlsx
+++ b/docs/StructureDefinition-cumulative-stress-burden.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/StructureDefinition/cumulative-stress-burden</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/cumulative-stress-burden</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -468,7 +471,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -790,7 +793,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/aerospace-behavioral-state-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/aerospace-behavioral-state-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1204,7 +1207,7 @@
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
-    <t>stress units</t>
+    <t>score</t>
   </si>
   <si>
     <t>Quantity.unit</t>
@@ -1791,7 +1794,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.org/fhir/uv/aerospace/CodeSystem/aerospace-behavioral-state-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/aerospace-behavioral-state-cs"/&gt;
     &lt;code value="mood-level"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1829,7 +1832,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.org/fhir/uv/aerospace/CodeSystem/aerospace-behavioral-state-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/aerospace-behavioral-state-cs"/&gt;
     &lt;code value="cognitive-readiness"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1867,7 +1870,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://hl7.org/fhir/uv/aerospace/CodeSystem/aerospace-behavioral-state-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/aerospace-behavioral-state-cs"/&gt;
     &lt;code value="social-connectedness"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2127,54 +2130,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2232,149 +2237,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2386,16 +2391,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2445,31 +2450,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2480,10 +2485,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2491,10 +2496,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2503,19 +2508,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2565,13 +2570,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2600,10 +2605,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2611,10 +2616,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2623,16 +2628,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2683,19 +2688,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2718,10 +2723,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2729,31 +2734,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2803,19 +2808,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2838,10 +2843,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2849,10 +2854,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2864,16 +2869,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2899,13 +2904,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2923,19 +2928,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2958,21 +2963,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2984,16 +2989,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3043,19 +3048,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -3067,7 +3072,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -3078,21 +3083,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -3104,16 +3109,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3163,13 +3168,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3187,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -3198,10 +3203,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3209,10 +3214,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3224,13 +3229,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3269,29 +3274,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3314,23 +3319,23 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -3342,13 +3347,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3399,19 +3404,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3434,45 +3439,45 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3521,19 +3526,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3545,7 +3550,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3556,10 +3561,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3567,10 +3572,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3579,20 +3584,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3641,34 +3646,34 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>20</v>
@@ -3676,21 +3681,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3699,20 +3704,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3761,31 +3766,31 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3796,21 +3801,21 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3819,19 +3824,19 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3881,31 +3886,31 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3927,34 +3932,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3979,13 +3984,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -4003,34 +4008,34 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -4038,10 +4043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4049,10 +4054,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -4064,19 +4069,19 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4101,13 +4106,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4125,19 +4130,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -4149,10 +4154,10 @@
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -4160,21 +4165,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -4183,22 +4188,22 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4223,13 +4228,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -4247,45 +4252,45 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4293,10 +4298,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -4308,13 +4313,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4365,13 +4370,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -4389,7 +4394,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4400,21 +4405,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4426,16 +4431,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4473,31 +4478,31 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4509,7 +4514,7 @@
         <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4520,10 +4525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4531,10 +4536,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4543,22 +4548,22 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4607,19 +4612,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -4628,10 +4633,10 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4642,10 +4647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4653,10 +4658,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4668,13 +4673,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4725,13 +4730,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4749,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4760,21 +4765,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4786,16 +4791,16 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4833,31 +4838,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4869,7 +4874,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4880,10 +4885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4891,10 +4896,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4903,29 +4908,29 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>20</v>
@@ -4967,19 +4972,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4988,10 +4993,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5002,10 +5007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5013,10 +5018,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -5025,19 +5030,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5087,19 +5092,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -5108,10 +5113,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5122,10 +5127,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5133,10 +5138,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -5145,27 +5150,27 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>20</v>
@@ -5207,19 +5212,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5228,10 +5233,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5242,10 +5247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5253,10 +5258,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5265,20 +5270,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5327,19 +5332,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -5348,10 +5353,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5362,10 +5367,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5373,10 +5378,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5385,22 +5390,22 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5449,19 +5454,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5470,10 +5475,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5484,10 +5489,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5495,10 +5500,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5507,22 +5512,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5571,19 +5576,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5592,10 +5597,10 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5606,10 +5611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5617,10 +5622,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5629,22 +5634,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5693,34 +5698,34 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5728,10 +5733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5739,10 +5744,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5751,19 +5756,19 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5813,34 +5818,34 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5848,21 +5853,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5871,22 +5876,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5935,34 +5940,34 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>20</v>
@@ -5970,21 +5975,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5993,22 +5998,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6057,34 +6062,34 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>20</v>
@@ -6092,10 +6097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6103,10 +6108,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -6115,19 +6120,19 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6177,19 +6182,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6198,13 +6203,13 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>20</v>
@@ -6212,10 +6217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6223,10 +6228,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6235,20 +6240,20 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6297,34 +6302,34 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>20</v>
@@ -6332,10 +6337,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6343,10 +6348,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6355,22 +6360,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6419,45 +6424,45 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6465,10 +6470,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6480,13 +6485,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6537,13 +6542,13 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -6561,7 +6566,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6572,21 +6577,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6598,16 +6603,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6645,31 +6650,31 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6681,7 +6686,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6692,10 +6697,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6703,10 +6708,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6715,22 +6720,22 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6779,19 +6784,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6800,10 +6805,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6814,10 +6819,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6825,38 +6830,38 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R39" t="s" s="2">
         <v>20</v>
@@ -6877,13 +6882,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6901,19 +6906,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6922,10 +6927,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6936,10 +6941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6947,10 +6952,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6959,20 +6964,20 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6982,7 +6987,7 @@
         <v>20</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>20</v>
@@ -7021,19 +7026,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -7042,10 +7047,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7056,10 +7061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7067,10 +7072,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -7079,20 +7084,20 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7141,19 +7146,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7162,10 +7167,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7176,10 +7181,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7187,10 +7192,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -7199,22 +7204,22 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7263,19 +7268,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -7284,10 +7289,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7298,10 +7303,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7309,10 +7314,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7324,19 +7329,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7361,13 +7366,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7385,19 +7390,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7406,10 +7411,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7420,21 +7425,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7446,19 +7451,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7483,13 +7488,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7507,45 +7512,45 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7553,10 +7558,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7568,19 +7573,19 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7629,19 +7634,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7650,10 +7655,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7664,10 +7669,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7675,10 +7680,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7690,16 +7695,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7725,13 +7730,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7749,45 +7754,45 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7795,10 +7800,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7810,19 +7815,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7847,13 +7852,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7871,19 +7876,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7892,10 +7897,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7906,10 +7911,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7917,10 +7922,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7932,16 +7937,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7991,45 +7996,45 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8037,10 +8042,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -8052,16 +8057,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8111,45 +8116,45 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8157,10 +8162,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8172,19 +8177,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8233,19 +8238,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8254,10 +8259,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8268,10 +8273,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8279,10 +8284,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8294,13 +8299,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8351,13 +8356,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -8375,7 +8380,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8386,21 +8391,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8412,16 +8417,16 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8471,19 +8476,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8495,7 +8500,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8506,45 +8511,45 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8593,19 +8598,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8617,7 +8622,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8628,10 +8633,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8639,10 +8644,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8654,13 +8659,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8711,19 +8716,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8732,10 +8737,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8746,10 +8751,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8757,10 +8762,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8772,13 +8777,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8829,19 +8834,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8850,10 +8855,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8864,10 +8869,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8875,10 +8880,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8890,19 +8895,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8927,13 +8932,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8951,31 +8956,31 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8986,10 +8991,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8997,10 +9002,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -9012,19 +9017,19 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9049,13 +9054,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -9073,31 +9078,31 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AN57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9108,10 +9113,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9119,10 +9124,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -9134,17 +9139,17 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9193,19 +9198,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9217,7 +9222,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9228,10 +9233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9239,10 +9244,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9254,13 +9259,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9311,19 +9316,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9332,10 +9337,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9346,10 +9351,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9357,10 +9362,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9369,19 +9374,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9431,19 +9436,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9452,10 +9457,10 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9466,10 +9471,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9477,10 +9482,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9489,19 +9494,19 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9551,19 +9556,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9572,10 +9577,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9586,10 +9591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9597,10 +9602,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9609,22 +9614,22 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9661,29 +9666,29 @@
         <v>20</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9692,10 +9697,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9706,10 +9711,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9717,10 +9722,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9732,13 +9737,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9789,13 +9794,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9813,7 +9818,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9824,21 +9829,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9850,16 +9855,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9909,19 +9914,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9933,7 +9938,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9944,45 +9949,45 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -10031,19 +10036,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -10055,7 +10060,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10066,10 +10071,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10077,10 +10082,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -10089,22 +10094,22 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10129,13 +10134,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -10153,34 +10158,34 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>20</v>
@@ -10188,10 +10193,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10199,10 +10204,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10211,22 +10216,22 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10275,45 +10280,45 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10321,10 +10326,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -10336,19 +10341,19 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10373,13 +10378,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -10397,19 +10402,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10418,10 +10423,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10432,21 +10437,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10458,19 +10463,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10495,13 +10500,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10519,45 +10524,45 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10565,10 +10570,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10580,19 +10585,19 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10641,19 +10646,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10662,10 +10667,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10676,23 +10681,23 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10701,22 +10706,22 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10765,19 +10770,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10786,10 +10791,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10800,10 +10805,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10811,10 +10816,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10826,13 +10831,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10883,13 +10888,13 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
@@ -10907,7 +10912,7 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10918,21 +10923,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10944,16 +10949,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11003,19 +11008,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -11027,7 +11032,7 @@
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11038,45 +11043,45 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11125,19 +11130,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11149,7 +11154,7 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11160,10 +11165,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11171,10 +11176,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -11183,22 +11188,22 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11208,7 +11213,7 @@
         <v>20</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>20</v>
@@ -11223,13 +11228,13 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11247,34 +11252,34 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>20</v>
@@ -11282,10 +11287,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11293,10 +11298,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11305,22 +11310,22 @@
         <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11369,45 +11374,45 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11415,10 +11420,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11430,19 +11435,19 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11467,13 +11472,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -11491,19 +11496,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11512,10 +11517,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11526,21 +11531,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -11552,19 +11557,19 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11589,13 +11594,13 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -11613,45 +11618,45 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11659,10 +11664,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11674,19 +11679,19 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11735,19 +11740,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11756,10 +11761,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11770,23 +11775,23 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11795,22 +11800,22 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11859,19 +11864,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -11880,10 +11885,10 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -11894,10 +11899,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11905,10 +11910,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11920,13 +11925,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11977,13 +11982,13 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
@@ -12001,7 +12006,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12012,21 +12017,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -12038,16 +12043,16 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12097,19 +12102,19 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -12121,7 +12126,7 @@
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12132,45 +12137,45 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12219,19 +12224,19 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
@@ -12243,7 +12248,7 @@
         <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12254,10 +12259,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12265,10 +12270,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -12277,22 +12282,22 @@
         <v>20</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12302,7 +12307,7 @@
         <v>20</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>20</v>
@@ -12317,13 +12322,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -12341,34 +12346,34 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>20</v>
@@ -12376,10 +12381,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12387,10 +12392,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -12399,22 +12404,22 @@
         <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12463,45 +12468,45 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12509,10 +12514,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -12524,19 +12529,19 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12561,13 +12566,13 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
@@ -12585,19 +12590,19 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12606,10 +12611,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12620,21 +12625,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
@@ -12646,19 +12651,19 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12683,13 +12688,13 @@
         <v>20</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
@@ -12707,45 +12712,45 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12753,10 +12758,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -12768,19 +12773,19 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12829,19 +12834,19 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -12850,10 +12855,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12864,23 +12869,23 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -12889,22 +12894,22 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12953,19 +12958,19 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -12974,10 +12979,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -12988,10 +12993,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12999,10 +13004,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -13014,13 +13019,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13071,13 +13076,13 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>20</v>
@@ -13095,7 +13100,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13106,21 +13111,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -13132,16 +13137,16 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13191,19 +13196,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -13215,7 +13220,7 @@
         <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13226,45 +13231,45 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13313,19 +13318,19 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
@@ -13337,7 +13342,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13348,10 +13353,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13359,10 +13364,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
@@ -13371,22 +13376,22 @@
         <v>20</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13396,7 +13401,7 @@
         <v>20</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>20</v>
@@ -13411,13 +13416,13 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -13435,34 +13440,34 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>20</v>
@@ -13470,10 +13475,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13481,10 +13486,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>20</v>
@@ -13493,22 +13498,22 @@
         <v>20</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13557,45 +13562,45 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13603,10 +13608,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
@@ -13618,19 +13623,19 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13655,13 +13660,13 @@
         <v>20</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
@@ -13679,19 +13684,19 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>20</v>
@@ -13700,10 +13705,10 @@
         <v>20</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -13714,21 +13719,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -13740,19 +13745,19 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13777,13 +13782,13 @@
         <v>20</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>20</v>
@@ -13801,45 +13806,45 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13847,10 +13852,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>20</v>
@@ -13862,19 +13867,19 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13923,19 +13928,19 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
@@ -13944,10 +13949,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
